--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O507"/>
+  <dimension ref="A1:O511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26311,6 +26311,210 @@
       <c r="O507" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>399.96</v>
+      </c>
+      <c r="C508" t="n">
+        <v>391.24</v>
+      </c>
+      <c r="D508" t="n">
+        <v>397.35</v>
+      </c>
+      <c r="E508" t="n">
+        <v>396.62</v>
+      </c>
+      <c r="F508" t="n">
+        <v>396.15</v>
+      </c>
+      <c r="G508" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="H508" t="n">
+        <v>392.91</v>
+      </c>
+      <c r="I508" t="n">
+        <v>389.98</v>
+      </c>
+      <c r="J508" t="n">
+        <v>390.35</v>
+      </c>
+      <c r="K508" t="n">
+        <v>386.41</v>
+      </c>
+      <c r="L508" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="M508" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="N508" t="n">
+        <v>388.76</v>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>401.06</v>
+      </c>
+      <c r="C509" t="n">
+        <v>392.65</v>
+      </c>
+      <c r="D509" t="n">
+        <v>398.55</v>
+      </c>
+      <c r="E509" t="n">
+        <v>397.43</v>
+      </c>
+      <c r="F509" t="n">
+        <v>397.24</v>
+      </c>
+      <c r="G509" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="H509" t="n">
+        <v>393.33</v>
+      </c>
+      <c r="I509" t="n">
+        <v>390.57</v>
+      </c>
+      <c r="J509" t="n">
+        <v>391.08</v>
+      </c>
+      <c r="K509" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="L509" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="M509" t="n">
+        <v>391.61</v>
+      </c>
+      <c r="N509" t="n">
+        <v>390.87</v>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>401.06</v>
+      </c>
+      <c r="C510" t="n">
+        <v>392.99</v>
+      </c>
+      <c r="D510" t="n">
+        <v>398.89</v>
+      </c>
+      <c r="E510" t="n">
+        <v>397.64</v>
+      </c>
+      <c r="F510" t="n">
+        <v>397.37</v>
+      </c>
+      <c r="G510" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="H510" t="n">
+        <v>393.02</v>
+      </c>
+      <c r="I510" t="n">
+        <v>390.76</v>
+      </c>
+      <c r="J510" t="n">
+        <v>391.37</v>
+      </c>
+      <c r="K510" t="n">
+        <v>388.29</v>
+      </c>
+      <c r="L510" t="n">
+        <v>386.41</v>
+      </c>
+      <c r="M510" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="N510" t="n">
+        <v>391.54</v>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>401.14</v>
+      </c>
+      <c r="C511" t="n">
+        <v>393.37</v>
+      </c>
+      <c r="D511" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>398.35</v>
+      </c>
+      <c r="F511" t="n">
+        <v>398.1</v>
+      </c>
+      <c r="G511" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="H511" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="I511" t="n">
+        <v>391.4</v>
+      </c>
+      <c r="J511" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="K511" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="L511" t="n">
+        <v>386.19</v>
+      </c>
+      <c r="M511" t="n">
+        <v>392.18</v>
+      </c>
+      <c r="N511" t="n">
+        <v>390.94</v>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31918,6 +32122,46 @@
       </c>
       <c r="B559" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -32086,28 +32330,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3551820252505573</v>
+        <v>0.3528710452254251</v>
       </c>
       <c r="J2" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1670207158600101</v>
+        <v>0.1674758995046619</v>
       </c>
       <c r="M2" t="n">
-        <v>4.906576211132101</v>
+        <v>4.879220628870428</v>
       </c>
       <c r="N2" t="n">
-        <v>39.0030713146898</v>
+        <v>38.71864662853591</v>
       </c>
       <c r="O2" t="n">
-        <v>6.245243895532807</v>
+        <v>6.222430925975468</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8323511735397</v>
+        <v>392.8554812458905</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32164,28 +32408,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2841696189059957</v>
+        <v>0.2818417775759972</v>
       </c>
       <c r="J3" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1556493028073518</v>
+        <v>0.1555838302673698</v>
       </c>
       <c r="M3" t="n">
-        <v>4.071886357068922</v>
+        <v>4.051932867663841</v>
       </c>
       <c r="N3" t="n">
-        <v>27.15588524993621</v>
+        <v>26.96785757041803</v>
       </c>
       <c r="O3" t="n">
-        <v>5.211130899328495</v>
+        <v>5.193058594934014</v>
       </c>
       <c r="P3" t="n">
-        <v>386.5164610180796</v>
+        <v>386.5397547284073</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32242,28 +32486,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3585541235938981</v>
+        <v>0.357226732693102</v>
       </c>
       <c r="J4" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K4" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2243589087820446</v>
+        <v>0.2259379861527988</v>
       </c>
       <c r="M4" t="n">
-        <v>3.953650725803114</v>
+        <v>3.929155568883115</v>
       </c>
       <c r="N4" t="n">
-        <v>27.55243085649837</v>
+        <v>27.34752513405462</v>
       </c>
       <c r="O4" t="n">
-        <v>5.24904094635376</v>
+        <v>5.229486125237797</v>
       </c>
       <c r="P4" t="n">
-        <v>389.8297106282535</v>
+        <v>389.8429883096809</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32320,28 +32564,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3713761051571911</v>
+        <v>0.3674506295480064</v>
       </c>
       <c r="J5" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K5" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L5" t="n">
-        <v>0.257740915509593</v>
+        <v>0.2564400108142147</v>
       </c>
       <c r="M5" t="n">
-        <v>3.777656399190601</v>
+        <v>3.768757928268575</v>
       </c>
       <c r="N5" t="n">
-        <v>24.62255168445541</v>
+        <v>24.48904463281801</v>
       </c>
       <c r="O5" t="n">
-        <v>4.962111615477368</v>
+        <v>4.948640685361791</v>
       </c>
       <c r="P5" t="n">
-        <v>390.2205159019817</v>
+        <v>390.2598079840819</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32398,28 +32642,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3563450666361752</v>
+        <v>0.3537203465046306</v>
       </c>
       <c r="J6" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K6" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2411471752473066</v>
+        <v>0.2413136992907328</v>
       </c>
       <c r="M6" t="n">
-        <v>3.904618329216976</v>
+        <v>3.886656909430412</v>
       </c>
       <c r="N6" t="n">
-        <v>24.77136085253781</v>
+        <v>24.60616737022299</v>
       </c>
       <c r="O6" t="n">
-        <v>4.977083568972677</v>
+        <v>4.960460399017715</v>
       </c>
       <c r="P6" t="n">
-        <v>389.430847720425</v>
+        <v>389.4571154018202</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32476,28 +32720,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2910717159582799</v>
+        <v>0.2848817953851324</v>
       </c>
       <c r="J7" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K7" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1884570467112312</v>
+        <v>0.1835426526381541</v>
       </c>
       <c r="M7" t="n">
-        <v>3.750100109509598</v>
+        <v>3.753965581579458</v>
       </c>
       <c r="N7" t="n">
-        <v>22.61685068920324</v>
+        <v>22.58236997181316</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75571768392566</v>
+        <v>4.752091115689299</v>
       </c>
       <c r="P7" t="n">
-        <v>388.666329929317</v>
+        <v>388.7282948380671</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32554,28 +32798,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2781141576902274</v>
+        <v>0.2725297434677283</v>
       </c>
       <c r="J8" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1858621079826123</v>
+        <v>0.1814864922012769</v>
       </c>
       <c r="M8" t="n">
-        <v>3.472531395255787</v>
+        <v>3.471086930247418</v>
       </c>
       <c r="N8" t="n">
-        <v>21.00323993780583</v>
+        <v>20.95332669597708</v>
       </c>
       <c r="O8" t="n">
-        <v>4.582929187518156</v>
+        <v>4.577480387284809</v>
       </c>
       <c r="P8" t="n">
-        <v>389.4990148513901</v>
+        <v>389.5549236283107</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32632,28 +32876,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2137506904747959</v>
+        <v>0.2078379745237549</v>
       </c>
       <c r="J9" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K9" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1041165665119748</v>
+        <v>0.1000285823162792</v>
       </c>
       <c r="M9" t="n">
-        <v>3.943922541756447</v>
+        <v>3.942226098083335</v>
       </c>
       <c r="N9" t="n">
-        <v>24.37135686924496</v>
+        <v>24.31073174314729</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9367354465522</v>
+        <v>4.930591419205945</v>
       </c>
       <c r="P9" t="n">
-        <v>389.0141066905517</v>
+        <v>389.0732965759355</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32710,28 +32954,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1270052651042297</v>
+        <v>0.1218760717520616</v>
       </c>
       <c r="J10" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K10" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03888816679267526</v>
+        <v>0.0363693651899295</v>
       </c>
       <c r="M10" t="n">
-        <v>4.030138235878602</v>
+        <v>4.02485899779097</v>
       </c>
       <c r="N10" t="n">
-        <v>24.71342243462301</v>
+        <v>24.61814914170673</v>
       </c>
       <c r="O10" t="n">
-        <v>4.971259642648231</v>
+        <v>4.96166797979336</v>
       </c>
       <c r="P10" t="n">
-        <v>391.2437627969251</v>
+        <v>391.2951082654382</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32788,28 +33032,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0608393780590499</v>
+        <v>0.0574476928121533</v>
       </c>
       <c r="J11" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K11" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01044946875600994</v>
+        <v>0.009464312168773303</v>
       </c>
       <c r="M11" t="n">
-        <v>3.813079570048223</v>
+        <v>3.801351767282519</v>
       </c>
       <c r="N11" t="n">
-        <v>21.72932744936831</v>
+        <v>21.60577648290876</v>
       </c>
       <c r="O11" t="n">
-        <v>4.661472669593625</v>
+        <v>4.648201424519892</v>
       </c>
       <c r="P11" t="n">
-        <v>388.3378000811127</v>
+        <v>388.371746104272</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32866,28 +33110,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.122291039985362</v>
+        <v>0.1169711885999205</v>
       </c>
       <c r="J12" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K12" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03948825008826629</v>
+        <v>0.03667651665552529</v>
       </c>
       <c r="M12" t="n">
-        <v>3.908953835026031</v>
+        <v>3.907485802326358</v>
       </c>
       <c r="N12" t="n">
-        <v>22.55054584534283</v>
+        <v>22.47944045060076</v>
       </c>
       <c r="O12" t="n">
-        <v>4.748741501213014</v>
+        <v>4.741248828167613</v>
       </c>
       <c r="P12" t="n">
-        <v>386.2568527516358</v>
+        <v>386.3101084479599</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32944,28 +33188,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09989303473086071</v>
+        <v>0.0964438534005662</v>
       </c>
       <c r="J13" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K13" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02259518384100578</v>
+        <v>0.02140691834059227</v>
       </c>
       <c r="M13" t="n">
-        <v>4.169204983158441</v>
+        <v>4.151983960750987</v>
       </c>
       <c r="N13" t="n">
-        <v>26.75851439603164</v>
+        <v>26.59749417454789</v>
       </c>
       <c r="O13" t="n">
-        <v>5.172863268638718</v>
+        <v>5.157275848211717</v>
       </c>
       <c r="P13" t="n">
-        <v>391.5225641956126</v>
+        <v>391.5570870087049</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33022,28 +33266,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1516572100122073</v>
+        <v>0.1552225638630044</v>
       </c>
       <c r="J14" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K14" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04397105416414193</v>
+        <v>0.04663265101843039</v>
       </c>
       <c r="M14" t="n">
-        <v>4.549775710082784</v>
+        <v>4.532666486098218</v>
       </c>
       <c r="N14" t="n">
-        <v>31.00011300426061</v>
+        <v>30.81225611417033</v>
       </c>
       <c r="O14" t="n">
-        <v>5.567774510902953</v>
+        <v>5.550878859619469</v>
       </c>
       <c r="P14" t="n">
-        <v>383.9741134719744</v>
+        <v>383.9384032349654</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33081,7 +33325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O507"/>
+  <dimension ref="A1:O511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72123,6 +72367,314 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-34.99047197089791,173.45968121162622</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-34.99106194514695,173.46016509964988</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-34.991431997286206,173.460852023306</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-34.99171143424577,173.46162458629496</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-34.9919901595399,173.4624478722028</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-34.99229284455826,173.46326069624484</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-34.992523728140114,173.46409499700914</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-34.9927325654332,173.4649372948503</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>-34.992891462780314,173.46579413012248</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-34.993018466917036,173.46665773678296</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-34.99307910309488,173.46753916610578</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-34.99304796482442,173.4683770891873</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>-34.99284088866025,173.46918532914825</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-34.99046553875146,173.45969038681045</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-34.99105275436149,173.46017577521926</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-34.99142268642906,173.46085872270754</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-34.99170469505653,173.46162800850794</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-34.991981013805585,173.46245224694658</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-34.99228616218962,173.4632636955248</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-34.99252010803826,173.46409634912342</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-34.99272739729658,173.46493882936838</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-34.992884980626606,173.46579552212884</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-34.9930083240402,173.4666589198264</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-34.99307495873564,173.4675393753478</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-34.99303941260011,173.46837546091132</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>-34.99282287235774,173.4691778960604</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-34.99046553875146,173.45969038681045</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-34.99105053814359,173.46017834946966</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-34.991420048352786,173.46086062087102</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-34.991702947859295,173.46162889574825</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-34.99197992302992,173.46245276870496</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-34.99228565466796,173.4632639233182</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-34.9925227800182,173.46409535113432</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-34.992725732981384,173.46493932353516</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-34.99288240552444,173.46579607511762</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-34.99300159204227,173.46665970503204</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-34.99306820162818,173.4675397165032</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-34.99302836597698,173.46837335772202</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>-34.99281715154118,173.4691755357915</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-34.990465070958976,173.45969105409654</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-34.9910480611941,173.46018122657293</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-34.99141531533354,173.46086402639938</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-34.99169704066861,173.46163189546522</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-34.99197379790502,173.46245569857862</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-34.99228057945122,173.46326620125197</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-34.99252088377437,173.46409605938464</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-34.99272012686706,173.46494098809686</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-34.99287991921889,173.4657966090378</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-34.99300186132218,173.4666596736238</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-34.99307018371303,173.46753961643097</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-34.9930343347169,173.46837449412263</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-34.99282227466048,173.46917764946514</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26515,6 +26515,210 @@
       <c r="O511" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>400.65</v>
+      </c>
+      <c r="C512" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="D512" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="E512" t="n">
+        <v>399.34</v>
+      </c>
+      <c r="F512" t="n">
+        <v>399.03</v>
+      </c>
+      <c r="G512" t="n">
+        <v>393.15</v>
+      </c>
+      <c r="H512" t="n">
+        <v>393.48</v>
+      </c>
+      <c r="I512" t="n">
+        <v>391.46</v>
+      </c>
+      <c r="J512" t="n">
+        <v>392.29</v>
+      </c>
+      <c r="K512" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="L512" t="n">
+        <v>386.09</v>
+      </c>
+      <c r="M512" t="n">
+        <v>393.04</v>
+      </c>
+      <c r="N512" t="n">
+        <v>392.01</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>401.63</v>
+      </c>
+      <c r="C513" t="n">
+        <v>394.46</v>
+      </c>
+      <c r="D513" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="E513" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="F513" t="n">
+        <v>399.31</v>
+      </c>
+      <c r="G513" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="H513" t="n">
+        <v>394.06</v>
+      </c>
+      <c r="I513" t="n">
+        <v>391.64</v>
+      </c>
+      <c r="J513" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="K513" t="n">
+        <v>388.93</v>
+      </c>
+      <c r="L513" t="n">
+        <v>386.28</v>
+      </c>
+      <c r="M513" t="n">
+        <v>392.86</v>
+      </c>
+      <c r="N513" t="n">
+        <v>391.7</v>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="C514" t="n">
+        <v>394.39</v>
+      </c>
+      <c r="D514" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="E514" t="n">
+        <v>400.29</v>
+      </c>
+      <c r="F514" t="n">
+        <v>399.21</v>
+      </c>
+      <c r="G514" t="n">
+        <v>393.83</v>
+      </c>
+      <c r="H514" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="I514" t="n">
+        <v>391.51</v>
+      </c>
+      <c r="J514" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="K514" t="n">
+        <v>388.96</v>
+      </c>
+      <c r="L514" t="n">
+        <v>386.28</v>
+      </c>
+      <c r="M514" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="N514" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="C515" t="n">
+        <v>394.46</v>
+      </c>
+      <c r="D515" t="n">
+        <v>400.83</v>
+      </c>
+      <c r="E515" t="n">
+        <v>400.58</v>
+      </c>
+      <c r="F515" t="n">
+        <v>399.41</v>
+      </c>
+      <c r="G515" t="n">
+        <v>393.91</v>
+      </c>
+      <c r="H515" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="I515" t="n">
+        <v>391.41</v>
+      </c>
+      <c r="J515" t="n">
+        <v>393.29</v>
+      </c>
+      <c r="K515" t="n">
+        <v>389.64</v>
+      </c>
+      <c r="L515" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="M515" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="N515" t="n">
+        <v>391.74</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B563"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32162,6 +32366,46 @@
       </c>
       <c r="B563" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -32330,28 +32574,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3528710452254251</v>
+        <v>0.3514958659146065</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1674758995046619</v>
+        <v>0.1686723152202252</v>
       </c>
       <c r="M2" t="n">
-        <v>4.879220628870428</v>
+        <v>4.847819173023202</v>
       </c>
       <c r="N2" t="n">
-        <v>38.71864662853591</v>
+        <v>38.42601400016544</v>
       </c>
       <c r="O2" t="n">
-        <v>6.222430925975468</v>
+        <v>6.198871994174863</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8554812458905</v>
+        <v>392.8692994095281</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32408,28 +32652,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2818417775759972</v>
+        <v>0.2820867801815172</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1555838302673698</v>
+        <v>0.1580048301977901</v>
       </c>
       <c r="M3" t="n">
-        <v>4.051932867663841</v>
+        <v>4.022306567012687</v>
       </c>
       <c r="N3" t="n">
-        <v>26.96785757041803</v>
+        <v>26.75846277006497</v>
       </c>
       <c r="O3" t="n">
-        <v>5.193058594934014</v>
+        <v>5.17285827855983</v>
       </c>
       <c r="P3" t="n">
-        <v>386.5397547284073</v>
+        <v>386.5372892945321</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32486,28 +32730,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.357226732693102</v>
+        <v>0.3590163578272693</v>
       </c>
       <c r="J4" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2259379861527988</v>
+        <v>0.2305413498738884</v>
       </c>
       <c r="M4" t="n">
-        <v>3.929155568883115</v>
+        <v>3.909124368577053</v>
       </c>
       <c r="N4" t="n">
-        <v>27.34752513405462</v>
+        <v>27.14697133419522</v>
       </c>
       <c r="O4" t="n">
-        <v>5.229486125237797</v>
+        <v>5.210275552616696</v>
       </c>
       <c r="P4" t="n">
-        <v>389.8429883096809</v>
+        <v>389.8249951997593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32564,28 +32808,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3674506295480064</v>
+        <v>0.3673578446378993</v>
       </c>
       <c r="J5" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K5" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2564400108142147</v>
+        <v>0.2595060043891571</v>
       </c>
       <c r="M5" t="n">
-        <v>3.768757928268575</v>
+        <v>3.742182930776889</v>
       </c>
       <c r="N5" t="n">
-        <v>24.48904463281801</v>
+        <v>24.30016504603465</v>
       </c>
       <c r="O5" t="n">
-        <v>4.948640685361791</v>
+        <v>4.929519758154403</v>
       </c>
       <c r="P5" t="n">
-        <v>390.2598079840819</v>
+        <v>390.260733551515</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32642,28 +32886,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3537203465046306</v>
+        <v>0.3540306977848046</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K6" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2413136992907328</v>
+        <v>0.2446846218349357</v>
       </c>
       <c r="M6" t="n">
-        <v>3.886656909430412</v>
+        <v>3.858244125386803</v>
       </c>
       <c r="N6" t="n">
-        <v>24.60616737022299</v>
+        <v>24.4151811074778</v>
       </c>
       <c r="O6" t="n">
-        <v>4.960460399017715</v>
+        <v>4.941172037834526</v>
       </c>
       <c r="P6" t="n">
-        <v>389.4571154018202</v>
+        <v>389.4539937281905</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32720,28 +32964,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2848817953851324</v>
+        <v>0.2810171714097781</v>
       </c>
       <c r="J7" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K7" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1835426526381541</v>
+        <v>0.1815620627855048</v>
       </c>
       <c r="M7" t="n">
-        <v>3.753965581579458</v>
+        <v>3.745411174583476</v>
       </c>
       <c r="N7" t="n">
-        <v>22.58236997181316</v>
+        <v>22.46377891739166</v>
       </c>
       <c r="O7" t="n">
-        <v>4.752091115689299</v>
+        <v>4.739596915075339</v>
       </c>
       <c r="P7" t="n">
-        <v>388.7282948380671</v>
+        <v>388.7671426756254</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32798,28 +33042,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2725297434677283</v>
+        <v>0.268259924503279</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K8" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1814864922012769</v>
+        <v>0.178781401206804</v>
       </c>
       <c r="M8" t="n">
-        <v>3.471086930247418</v>
+        <v>3.463813552076763</v>
       </c>
       <c r="N8" t="n">
-        <v>20.95332669597708</v>
+        <v>20.85952872223201</v>
       </c>
       <c r="O8" t="n">
-        <v>4.577480387284809</v>
+        <v>4.5672233054923</v>
       </c>
       <c r="P8" t="n">
-        <v>389.5549236283107</v>
+        <v>389.5978456738839</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32876,28 +33120,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2078379745237549</v>
+        <v>0.2033138499181814</v>
       </c>
       <c r="J9" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K9" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1000285823162792</v>
+        <v>0.09730548749933043</v>
       </c>
       <c r="M9" t="n">
-        <v>3.942226098083335</v>
+        <v>3.933895891970741</v>
       </c>
       <c r="N9" t="n">
-        <v>24.31073174314729</v>
+        <v>24.19880133889533</v>
       </c>
       <c r="O9" t="n">
-        <v>4.930591419205945</v>
+        <v>4.919227717731242</v>
       </c>
       <c r="P9" t="n">
-        <v>389.0732965759355</v>
+        <v>389.1187794201797</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32954,28 +33198,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1218760717520616</v>
+        <v>0.1194452008271048</v>
       </c>
       <c r="J10" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0363693651899295</v>
+        <v>0.03551497271284765</v>
       </c>
       <c r="M10" t="n">
-        <v>4.02485899779097</v>
+        <v>4.005925082262555</v>
       </c>
       <c r="N10" t="n">
-        <v>24.61814914170673</v>
+        <v>24.4499441232063</v>
       </c>
       <c r="O10" t="n">
-        <v>4.96166797979336</v>
+        <v>4.944688475850253</v>
       </c>
       <c r="P10" t="n">
-        <v>391.2951082654382</v>
+        <v>391.3195415039759</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33032,28 +33276,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0574476928121533</v>
+        <v>0.05630807899084339</v>
       </c>
       <c r="J11" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K11" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009464312168773303</v>
+        <v>0.009244298182584654</v>
       </c>
       <c r="M11" t="n">
-        <v>3.801351767282519</v>
+        <v>3.777780945209411</v>
       </c>
       <c r="N11" t="n">
-        <v>21.60577648290876</v>
+        <v>21.44324528784836</v>
       </c>
       <c r="O11" t="n">
-        <v>4.648201424519892</v>
+        <v>4.630685185569017</v>
       </c>
       <c r="P11" t="n">
-        <v>388.371746104272</v>
+        <v>388.3831996174856</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33110,28 +33354,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1169711885999205</v>
+        <v>0.1126070822302105</v>
       </c>
       <c r="J12" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K12" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03667651665552529</v>
+        <v>0.03452429217481912</v>
       </c>
       <c r="M12" t="n">
-        <v>3.907485802326358</v>
+        <v>3.900717140924723</v>
       </c>
       <c r="N12" t="n">
-        <v>22.47944045060076</v>
+        <v>22.3771325895505</v>
       </c>
       <c r="O12" t="n">
-        <v>4.741248828167613</v>
+        <v>4.730447398455087</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3101084479599</v>
+        <v>386.3539777800835</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33188,28 +33432,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0964438534005662</v>
+        <v>0.0949810845674912</v>
       </c>
       <c r="J13" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K13" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02140691834059227</v>
+        <v>0.02110913240948709</v>
       </c>
       <c r="M13" t="n">
-        <v>4.151983960750987</v>
+        <v>4.126195535372069</v>
       </c>
       <c r="N13" t="n">
-        <v>26.59749417454789</v>
+        <v>26.39943291098581</v>
       </c>
       <c r="O13" t="n">
-        <v>5.157275848211717</v>
+        <v>5.138037846394848</v>
       </c>
       <c r="P13" t="n">
-        <v>391.5570870087049</v>
+        <v>391.5717895313002</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33266,28 +33510,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1552225638630044</v>
+        <v>0.1602754953616638</v>
       </c>
       <c r="J14" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K14" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04663265101843039</v>
+        <v>0.05020174452777937</v>
       </c>
       <c r="M14" t="n">
-        <v>4.532666486098218</v>
+        <v>4.523584222085671</v>
       </c>
       <c r="N14" t="n">
-        <v>30.81225611417033</v>
+        <v>30.66925808929443</v>
       </c>
       <c r="O14" t="n">
-        <v>5.550878859619469</v>
+        <v>5.537983214970449</v>
       </c>
       <c r="P14" t="n">
-        <v>383.9384032349654</v>
+        <v>383.8876081855711</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33325,7 +33569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72675,6 +72919,314 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-34.99046793618794,173.4596869669692</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-34.99104382430665,173.4601861479333</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-34.99140755628539,173.46086960923185</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-34.99168880388146,173.46163607816845</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-34.991965994663566,173.4624594311568</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-34.992278464777556,173.46326715039098</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-34.992518815144756,173.46409683202134</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-34.99271960129384,173.4649411441495</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-34.992874236234776,173.4657978294266</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-34.992995667884074,173.4666603960129</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-34.9930710846607,173.46753957094356</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-34.99302667334924,173.46837303545922</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-34.992813138431046,173.4691738800807</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-34.990462205729855,173.45969514122356</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-34.99104095625966,173.4601894793155</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-34.991404219894605,173.46087200984948</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-34.991680816693794,173.4616401341223</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-34.99196364530053,173.46246055494362</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-34.992271782408764,173.46327014966985</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-34.99251381595647,173.46409869922653</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-34.992718024574174,173.46494161230743</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-34.992867221301246,173.46579933584383</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-34.99299584740403,173.4666603750741</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-34.993069372860134,173.4675396573696</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-34.993028276891316,173.46837334076085</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-34.992815785376024,173.46917497214525</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-34.990461679463266,173.45969589192032</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-34.991041412539865,173.46018894932288</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-34.991405228570876,173.46087128408138</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-34.991680899893666,173.46164009187277</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-34.99196448435875,173.46246015359117</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-34.99227271286518,173.4632697320488</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-34.992514160728064,173.46409857045376</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-34.99271916331615,173.46494127419336</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-34.99286926362368,173.4657988972667</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-34.9929955781241,173.4666604064823</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-34.993069372860134,173.4675396573696</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-34.99302756420596,173.46837320507123</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-34.992818859247635,173.46917624034936</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-34.990461679463266,173.45969589192032</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-34.99104095625966,173.4601894793155</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-34.99140499579943,173.4608714515663</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-34.99167848709735,173.46164131710867</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-34.9919628062423,173.46246095629607</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-34.9922720361696,173.4632700357732</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-34.99251347118486,173.4640988279993</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-34.99272003927152,173.46494101410562</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-34.992865356572075,173.4657997362838</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-34.99298947444598,173.46666111840193</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-34.993063516700346,173.4675399530376</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-34.99302079369499,173.46837191602006</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-34.99281544383474,173.4691748312337</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26717,6 +26717,108 @@
         <v>391.74</v>
       </c>
       <c r="O515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>401.15</v>
+      </c>
+      <c r="C516" t="n">
+        <v>394.31</v>
+      </c>
+      <c r="D516" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="E516" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="F516" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="G516" t="n">
+        <v>393.67</v>
+      </c>
+      <c r="H516" t="n">
+        <v>393.63</v>
+      </c>
+      <c r="I516" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="J516" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="K516" t="n">
+        <v>389.81</v>
+      </c>
+      <c r="L516" t="n">
+        <v>387.03</v>
+      </c>
+      <c r="M516" t="n">
+        <v>394.53</v>
+      </c>
+      <c r="N516" t="n">
+        <v>392.05</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>400.84</v>
+      </c>
+      <c r="C517" t="n">
+        <v>394.38</v>
+      </c>
+      <c r="D517" t="n">
+        <v>401.71</v>
+      </c>
+      <c r="E517" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="F517" t="n">
+        <v>400.74</v>
+      </c>
+      <c r="G517" t="n">
+        <v>394.27</v>
+      </c>
+      <c r="H517" t="n">
+        <v>393.96</v>
+      </c>
+      <c r="I517" t="n">
+        <v>391.23</v>
+      </c>
+      <c r="J517" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="K517" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="L517" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="M517" t="n">
+        <v>393.71</v>
+      </c>
+      <c r="N517" t="n">
+        <v>391.43</v>
+      </c>
+      <c r="O517" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26733,7 +26835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32406,6 +32508,26 @@
       </c>
       <c r="B567" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -32574,28 +32696,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3514958659146065</v>
+        <v>0.3504929109823881</v>
       </c>
       <c r="J2" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K2" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1686723152202252</v>
+        <v>0.1689986770844955</v>
       </c>
       <c r="M2" t="n">
-        <v>4.847819173023202</v>
+        <v>4.833752151669227</v>
       </c>
       <c r="N2" t="n">
-        <v>38.42601400016544</v>
+        <v>38.28488172178187</v>
       </c>
       <c r="O2" t="n">
-        <v>6.198871994174863</v>
+        <v>6.187477815861797</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8692994095281</v>
+        <v>392.8794331312119</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32652,28 +32774,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2820867801815172</v>
+        <v>0.2821920287808044</v>
       </c>
       <c r="J3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1580048301977901</v>
+        <v>0.1592041736085081</v>
       </c>
       <c r="M3" t="n">
-        <v>4.022306567012687</v>
+        <v>4.007308860175207</v>
       </c>
       <c r="N3" t="n">
-        <v>26.75846277006497</v>
+        <v>26.65483539331066</v>
       </c>
       <c r="O3" t="n">
-        <v>5.17285827855983</v>
+        <v>5.162832109734991</v>
       </c>
       <c r="P3" t="n">
-        <v>386.5372892945321</v>
+        <v>386.5362257756739</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32730,28 +32852,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3590163578272693</v>
+        <v>0.360252583094586</v>
       </c>
       <c r="J4" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K4" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2305413498738884</v>
+        <v>0.2331534360853147</v>
       </c>
       <c r="M4" t="n">
-        <v>3.909124368577053</v>
+        <v>3.901232080731637</v>
       </c>
       <c r="N4" t="n">
-        <v>27.14697133419522</v>
+        <v>27.05398752218604</v>
       </c>
       <c r="O4" t="n">
-        <v>5.210275552616696</v>
+        <v>5.201344780168495</v>
       </c>
       <c r="P4" t="n">
-        <v>389.8249951997593</v>
+        <v>389.812502755095</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32808,28 +32930,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3673578446378993</v>
+        <v>0.3679765355579031</v>
       </c>
       <c r="J5" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K5" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2595060043891571</v>
+        <v>0.2617087733962794</v>
       </c>
       <c r="M5" t="n">
-        <v>3.742182930776889</v>
+        <v>3.731071751995214</v>
       </c>
       <c r="N5" t="n">
-        <v>24.30016504603465</v>
+        <v>24.21029609008512</v>
       </c>
       <c r="O5" t="n">
-        <v>4.929519758154403</v>
+        <v>4.920395928183535</v>
       </c>
       <c r="P5" t="n">
-        <v>390.260733551515</v>
+        <v>390.2544771379449</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32886,28 +33008,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3540306977848046</v>
+        <v>0.3547750089517366</v>
       </c>
       <c r="J6" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K6" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2446846218349357</v>
+        <v>0.246948615691443</v>
       </c>
       <c r="M6" t="n">
-        <v>3.858244125386803</v>
+        <v>3.847666731350437</v>
       </c>
       <c r="N6" t="n">
-        <v>24.4151811074778</v>
+        <v>24.32621144147303</v>
       </c>
       <c r="O6" t="n">
-        <v>4.941172037834526</v>
+        <v>4.932160930208283</v>
       </c>
       <c r="P6" t="n">
-        <v>389.4539937281905</v>
+        <v>389.4464682042146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32964,28 +33086,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2810171714097781</v>
+        <v>0.2793019010391574</v>
       </c>
       <c r="J7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1815620627855048</v>
+        <v>0.1808169667434855</v>
       </c>
       <c r="M7" t="n">
-        <v>3.745411174583476</v>
+        <v>3.739947029074869</v>
       </c>
       <c r="N7" t="n">
-        <v>22.46377891739166</v>
+        <v>22.39958515808626</v>
       </c>
       <c r="O7" t="n">
-        <v>4.739596915075339</v>
+        <v>4.732820000600727</v>
       </c>
       <c r="P7" t="n">
-        <v>388.7671426756254</v>
+        <v>388.7844673988533</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33042,28 +33164,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.268259924503279</v>
+        <v>0.2660774961479859</v>
       </c>
       <c r="J8" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K8" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L8" t="n">
-        <v>0.178781401206804</v>
+        <v>0.177339567629297</v>
       </c>
       <c r="M8" t="n">
-        <v>3.463813552076763</v>
+        <v>3.460334569599642</v>
       </c>
       <c r="N8" t="n">
-        <v>20.85952872223201</v>
+        <v>20.81525219279754</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5672233054923</v>
+        <v>4.562373526224869</v>
       </c>
       <c r="P8" t="n">
-        <v>389.5978456738839</v>
+        <v>389.6198910899349</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33120,28 +33242,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2033138499181814</v>
+        <v>0.2006994976208805</v>
       </c>
       <c r="J9" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K9" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09730548749933043</v>
+        <v>0.09557824180462493</v>
       </c>
       <c r="M9" t="n">
-        <v>3.933895891970741</v>
+        <v>3.931483040953574</v>
       </c>
       <c r="N9" t="n">
-        <v>24.19880133889533</v>
+        <v>24.15766519946784</v>
       </c>
       <c r="O9" t="n">
-        <v>4.919227717731242</v>
+        <v>4.915044781023652</v>
       </c>
       <c r="P9" t="n">
-        <v>389.1187794201797</v>
+        <v>389.1451868809382</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33198,28 +33320,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1194452008271048</v>
+        <v>0.1184033665807024</v>
       </c>
       <c r="J10" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K10" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03551497271284765</v>
+        <v>0.03518687588504177</v>
       </c>
       <c r="M10" t="n">
-        <v>4.005925082262555</v>
+        <v>3.995666550023596</v>
       </c>
       <c r="N10" t="n">
-        <v>24.4499441232063</v>
+        <v>24.3635751593439</v>
       </c>
       <c r="O10" t="n">
-        <v>4.944688475850253</v>
+        <v>4.935947240332285</v>
       </c>
       <c r="P10" t="n">
-        <v>391.3195415039759</v>
+        <v>391.3300646621635</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33276,28 +33398,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05630807899084339</v>
+        <v>0.05632531095125016</v>
       </c>
       <c r="J11" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K11" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009244298182584654</v>
+        <v>0.009325740356200707</v>
       </c>
       <c r="M11" t="n">
-        <v>3.777780945209411</v>
+        <v>3.763620782497673</v>
       </c>
       <c r="N11" t="n">
-        <v>21.44324528784836</v>
+        <v>21.36019326648159</v>
       </c>
       <c r="O11" t="n">
-        <v>4.630685185569017</v>
+        <v>4.621708911915764</v>
       </c>
       <c r="P11" t="n">
-        <v>388.3831996174856</v>
+        <v>388.3830242352589</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33354,28 +33476,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1126070822302105</v>
+        <v>0.1111057092894957</v>
       </c>
       <c r="J12" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K12" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03452429217481912</v>
+        <v>0.03388391363299481</v>
       </c>
       <c r="M12" t="n">
-        <v>3.900717140924723</v>
+        <v>3.893641718346287</v>
       </c>
       <c r="N12" t="n">
-        <v>22.3771325895505</v>
+        <v>22.30791199140862</v>
       </c>
       <c r="O12" t="n">
-        <v>4.730447398455087</v>
+        <v>4.723125235626155</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3539777800835</v>
+        <v>386.3691421472528</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33432,28 +33554,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0949810845674912</v>
+        <v>0.09495743818728589</v>
       </c>
       <c r="J13" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K13" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02110913240948709</v>
+        <v>0.02126927577107562</v>
       </c>
       <c r="M13" t="n">
-        <v>4.126195535372069</v>
+        <v>4.111775038469457</v>
       </c>
       <c r="N13" t="n">
-        <v>26.39943291098581</v>
+        <v>26.29776991409007</v>
       </c>
       <c r="O13" t="n">
-        <v>5.138037846394848</v>
+        <v>5.128135130248624</v>
       </c>
       <c r="P13" t="n">
-        <v>391.5717895313002</v>
+        <v>391.5720327519234</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33510,28 +33632,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1602754953616638</v>
+        <v>0.162748440757725</v>
       </c>
       <c r="J14" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K14" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05020174452777937</v>
+        <v>0.05201152464366754</v>
       </c>
       <c r="M14" t="n">
-        <v>4.523584222085671</v>
+        <v>4.518793367941195</v>
       </c>
       <c r="N14" t="n">
-        <v>30.66925808929443</v>
+        <v>30.59761449245674</v>
       </c>
       <c r="O14" t="n">
-        <v>5.537983214970449</v>
+        <v>5.531511049655125</v>
       </c>
       <c r="P14" t="n">
-        <v>383.8876081855711</v>
+        <v>383.8626295861928</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33569,7 +33691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73227,6 +73349,160 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-34.990465012484904,173.4596911375073</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-34.99104193400295,173.46018834361703</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-34.991404219894605,173.46087200984948</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-34.99167923589621,173.46164093686306</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-34.991962051089885,173.46246131751323</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-34.99227406625634,173.46326912459992</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-34.992517522251234,173.46409731491926</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-34.9927266965323,173.4649390374386</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-34.992868464454034,173.46579906888385</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-34.99298794852645,173.4666612963818</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-34.99306261575268,173.46753999852498</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-34.9930133995843,173.4683705082407</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-34.992812796889744,173.46917373916915</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-34.9904668251808,173.45968855177372</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-34.991041477722746,173.46018887360964</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-34.99139816783676,173.4608763644577</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-34.991669002311774,173.4616461335526</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-34.99195164676771,173.46246629428254</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-34.992268991039495,173.46327140253305</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-34.99251467788549,173.46409837729462</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-34.99272161599119,173.46494054594768</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-34.9928658005552,173.46579964094096</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-34.992985704527115,173.46666155811693</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-34.99305802091959,173.46754023051062</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-34.99302070460931,173.46837189905884</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-34.99281809077972,173.46917592329834</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
